--- a/labeled/Add_Eating/July/multi_seed_results/seed_101/predictions.xlsx
+++ b/labeled/Add_Eating/July/multi_seed_results/seed_101/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B146"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,1162 +442,746 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>25.79999923706055</v>
+        <v>44.79999923706055</v>
       </c>
       <c r="B2" t="n">
-        <v>31.76570320129395</v>
+        <v>40.59139251708984</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>28.20763969421387</v>
+        <v>34.02777862548828</v>
       </c>
       <c r="B3" t="n">
-        <v>21.14859008789062</v>
+        <v>36.58949661254883</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9.960552215576172</v>
+        <v>73.5</v>
       </c>
       <c r="B4" t="n">
-        <v>11.50068759918213</v>
+        <v>72.91013336181641</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6.660137176513672</v>
+        <v>12.73261547088623</v>
       </c>
       <c r="B5" t="n">
-        <v>10.76396179199219</v>
+        <v>12.43985366821289</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>46.70000076293945</v>
+        <v>14.58333301544189</v>
       </c>
       <c r="B6" t="n">
-        <v>33.01401519775391</v>
+        <v>15.17318725585938</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20.27424049377441</v>
+        <v>16.5714282989502</v>
       </c>
       <c r="B7" t="n">
-        <v>24.09049415588379</v>
+        <v>11.95388698577881</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10.34482765197754</v>
+        <v>14.39764976501465</v>
       </c>
       <c r="B8" t="n">
-        <v>7.564126014709473</v>
+        <v>11.50030136108398</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>14.1304349899292</v>
+        <v>13.71204662322998</v>
       </c>
       <c r="B9" t="n">
-        <v>11.0509614944458</v>
+        <v>17.71183776855469</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6.502462863922119</v>
+        <v>10.2857141494751</v>
       </c>
       <c r="B10" t="n">
-        <v>5.736232757568359</v>
+        <v>12.98460960388184</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>14.20176315307617</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="B11" t="n">
-        <v>15.78137016296387</v>
+        <v>11.8466968536377</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>30.66666603088379</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="B12" t="n">
-        <v>23.68817138671875</v>
+        <v>29.38400840759277</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12.99603176116943</v>
+        <v>36.5</v>
       </c>
       <c r="B13" t="n">
-        <v>16.94644737243652</v>
+        <v>35.45930862426758</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11.70634937286377</v>
+        <v>20.33730125427246</v>
       </c>
       <c r="B14" t="n">
-        <v>9.398049354553223</v>
+        <v>14.52284049987793</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>27.32615089416504</v>
+        <v>25.6611156463623</v>
       </c>
       <c r="B15" t="n">
-        <v>25.95992279052734</v>
+        <v>30.16543006896973</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12.54940700531006</v>
+        <v>6.646825313568115</v>
       </c>
       <c r="B16" t="n">
-        <v>12.0529956817627</v>
+        <v>6.394946098327637</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>69.63761138916016</v>
+        <v>8.952381134033203</v>
       </c>
       <c r="B17" t="n">
-        <v>63.80052947998047</v>
+        <v>8.930239677429199</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>68.85713958740234</v>
+        <v>31.29999923706055</v>
       </c>
       <c r="B18" t="n">
-        <v>61.96037673950195</v>
+        <v>27.81286239624023</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>31</v>
+        <v>17.53183174133301</v>
       </c>
       <c r="B19" t="n">
-        <v>33.24053192138672</v>
+        <v>13.77811813354492</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>100</v>
+        <v>32.24206161499023</v>
       </c>
       <c r="B20" t="n">
-        <v>93.32678985595703</v>
+        <v>21.22765350341797</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16.56746101379395</v>
+        <v>12.30158710479736</v>
       </c>
       <c r="B21" t="n">
-        <v>12.26448440551758</v>
+        <v>11.80306625366211</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="B22" t="n">
-        <v>76.84622955322266</v>
+        <v>37.37487030029297</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>19.79999923706055</v>
+        <v>29.10000038146973</v>
       </c>
       <c r="B23" t="n">
-        <v>23.67647171020508</v>
+        <v>22.80596542358398</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>85.69999694824219</v>
+        <v>45.52381134033203</v>
       </c>
       <c r="B24" t="n">
-        <v>84.04013061523438</v>
+        <v>50.53792572021484</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>59.40000152587891</v>
+        <v>28.7952995300293</v>
       </c>
       <c r="B25" t="n">
-        <v>58.03199005126953</v>
+        <v>39.6762809753418</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>9.402546882629395</v>
+        <v>15.083251953125</v>
       </c>
       <c r="B26" t="n">
-        <v>9.72065258026123</v>
+        <v>12.34762382507324</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>8.275861740112305</v>
+        <v>13.89999961853027</v>
       </c>
       <c r="B27" t="n">
-        <v>32.09904861450195</v>
+        <v>16.55518341064453</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>15.46798038482666</v>
+        <v>21.29999923706055</v>
       </c>
       <c r="B28" t="n">
-        <v>24.34945869445801</v>
+        <v>18.73758697509766</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6.0724778175354</v>
+        <v>30.66666603088379</v>
       </c>
       <c r="B29" t="n">
-        <v>11.6755485534668</v>
+        <v>26.87601280212402</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>46.20000076293945</v>
+        <v>32.85714340209961</v>
       </c>
       <c r="B30" t="n">
-        <v>35.50264358520508</v>
+        <v>37.9488410949707</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>40.20000076293945</v>
+        <v>14.1304349899292</v>
       </c>
       <c r="B31" t="n">
-        <v>37.30419540405273</v>
+        <v>13.59166526794434</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>13.4285717010498</v>
+        <v>90.19999694824219</v>
       </c>
       <c r="B32" t="n">
-        <v>21.63973236083984</v>
+        <v>78.23391723632812</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>11.50793647766113</v>
+        <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>10.59164428710938</v>
+        <v>29.92287826538086</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>51.59999847412109</v>
+        <v>13.32027435302734</v>
       </c>
       <c r="B34" t="n">
-        <v>44.51733016967773</v>
+        <v>16.95766067504883</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>8.275861740112305</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="B35" t="n">
-        <v>32.09904861450195</v>
+        <v>21.30949592590332</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>60</v>
+        <v>5.320197105407715</v>
       </c>
       <c r="B36" t="n">
-        <v>51.92501068115234</v>
+        <v>15.70654582977295</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2.644466161727905</v>
+        <v>27.32615089416504</v>
       </c>
       <c r="B37" t="n">
-        <v>8.661255836486816</v>
+        <v>24.2447681427002</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>27.6785717010498</v>
+        <v>40.25465393066406</v>
       </c>
       <c r="B38" t="n">
-        <v>24.72492218017578</v>
+        <v>34.43801498413086</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38.09999847412109</v>
+        <v>23.80952453613281</v>
       </c>
       <c r="B39" t="n">
-        <v>39.89560317993164</v>
+        <v>18.6645679473877</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>58.76591491699219</v>
+        <v>24</v>
       </c>
       <c r="B40" t="n">
-        <v>63.3690185546875</v>
+        <v>25.85861396789551</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>21.47511672973633</v>
+        <v>42.10882949829102</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>8.630952835083008</v>
+        <v>20.38095283508301</v>
       </c>
       <c r="B42" t="n">
-        <v>11.40494823455811</v>
+        <v>25.68808746337891</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>25.79999923706055</v>
+        <v>57</v>
       </c>
       <c r="B43" t="n">
-        <v>31.76570320129395</v>
+        <v>40.09415054321289</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>19.09892272949219</v>
+        <v>9.027777671813965</v>
       </c>
       <c r="B44" t="n">
-        <v>15.61008071899414</v>
+        <v>14.88626861572266</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>12.53672885894775</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="B45" t="n">
-        <v>15.22390174865723</v>
+        <v>22.04469108581543</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>39.17727661132812</v>
+        <v>18.39999961853027</v>
       </c>
       <c r="B46" t="n">
-        <v>35.48429870605469</v>
+        <v>17.15338897705078</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>12.74703598022461</v>
+        <v>14.20176315307617</v>
       </c>
       <c r="B47" t="n">
-        <v>12.41061973571777</v>
+        <v>18.63577270507812</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>91.5</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="B48" t="n">
-        <v>84.14739227294922</v>
+        <v>24.03082656860352</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>18.31537628173828</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="B49" t="n">
-        <v>12.72358512878418</v>
+        <v>18.78072547912598</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>34.37805938720703</v>
+        <v>26.15083312988281</v>
       </c>
       <c r="B50" t="n">
-        <v>31.62886238098145</v>
+        <v>27.65968132019043</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131.6999969482422</v>
+        <v>29.60000038146973</v>
       </c>
       <c r="B51" t="n">
-        <v>123.6058654785156</v>
+        <v>19.53951644897461</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>28.7952995300293</v>
+        <v>22.33104705810547</v>
       </c>
       <c r="B52" t="n">
-        <v>30.65286445617676</v>
+        <v>12.20324897766113</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>5.320197105407715</v>
+        <v>10.4761905670166</v>
       </c>
       <c r="B53" t="n">
-        <v>5.131136417388916</v>
+        <v>10.51460933685303</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>24.19047546386719</v>
+        <v>20.47012710571289</v>
       </c>
       <c r="B54" t="n">
-        <v>22.6552562713623</v>
+        <v>23.22494697570801</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>30.55827713012695</v>
+        <v>28.40352630615234</v>
       </c>
       <c r="B55" t="n">
-        <v>31.84899139404297</v>
+        <v>23.85556602478027</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>97.94319152832031</v>
+        <v>14</v>
       </c>
       <c r="B56" t="n">
-        <v>89.77194213867188</v>
+        <v>19.39870452880859</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>59.52381134033203</v>
+        <v>18.55158805847168</v>
       </c>
       <c r="B57" t="n">
-        <v>54.84144592285156</v>
+        <v>24.96966361999512</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>22.09523773193359</v>
+        <v>33.79999923706055</v>
       </c>
       <c r="B58" t="n">
-        <v>24.748291015625</v>
+        <v>24.85439682006836</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>24.00793647766113</v>
+        <v>11.50793647766113</v>
       </c>
       <c r="B59" t="n">
-        <v>24.66971397399902</v>
+        <v>32.98405838012695</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>20</v>
+        <v>68.28571319580078</v>
       </c>
       <c r="B60" t="n">
-        <v>24.61632537841797</v>
+        <v>62.77225494384766</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>33.79999923706055</v>
+        <v>10.69999980926514</v>
       </c>
       <c r="B61" t="n">
-        <v>31.40835762023926</v>
+        <v>13.33194637298584</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>11.65524005889893</v>
+        <v>53.59999847412109</v>
       </c>
       <c r="B62" t="n">
-        <v>13.15082454681396</v>
+        <v>28.60451507568359</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>57.09999847412109</v>
+        <v>6.502462863922119</v>
       </c>
       <c r="B63" t="n">
-        <v>51.74006271362305</v>
+        <v>12.95285606384277</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>34.02777862548828</v>
+        <v>23.70000076293945</v>
       </c>
       <c r="B64" t="n">
-        <v>29.71552085876465</v>
+        <v>25.46687507629395</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>73.5</v>
+        <v>20.27424049377441</v>
       </c>
       <c r="B65" t="n">
-        <v>69.57109069824219</v>
+        <v>34.08662414550781</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>23.10000038146973</v>
+        <v>15.10000038146973</v>
       </c>
       <c r="B66" t="n">
-        <v>21.86330795288086</v>
+        <v>14.60567569732666</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>16.5714282989502</v>
+        <v>15.46798038482666</v>
       </c>
       <c r="B67" t="n">
-        <v>19.36524772644043</v>
+        <v>21.34223365783691</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>13.71204662322998</v>
+        <v>30.85210609436035</v>
       </c>
       <c r="B68" t="n">
-        <v>19.45672225952148</v>
+        <v>22.30398941040039</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>60</v>
+        <v>16.39999961853027</v>
       </c>
       <c r="B69" t="n">
-        <v>58.94499969482422</v>
+        <v>37.78958892822266</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>19.84127044677734</v>
+        <v>10.47992134094238</v>
       </c>
       <c r="B70" t="n">
-        <v>24.29294204711914</v>
+        <v>10.50629425048828</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>20.37218475341797</v>
+        <v>19.19686508178711</v>
       </c>
       <c r="B71" t="n">
-        <v>16.26984405517578</v>
+        <v>20.23014259338379</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>18.70000076293945</v>
+        <v>12.5</v>
       </c>
       <c r="B72" t="n">
-        <v>20.0245475769043</v>
+        <v>12.85146617889404</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>19.0476188659668</v>
+        <v>20.17629814147949</v>
       </c>
       <c r="B73" t="n">
-        <v>25.43822860717773</v>
+        <v>22.40610313415527</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>36.5</v>
+        <v>18.75</v>
       </c>
       <c r="B74" t="n">
-        <v>42.62878799438477</v>
+        <v>21.938232421875</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>39.5</v>
+        <v>11.10000038146973</v>
       </c>
       <c r="B75" t="n">
-        <v>40.34913635253906</v>
+        <v>23.17508697509766</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>17.94871711730957</v>
+        <v>36.63075256347656</v>
       </c>
       <c r="B76" t="n">
-        <v>14.49005317687988</v>
+        <v>17.88454437255859</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>39.17727661132812</v>
+        <v>21.5475025177002</v>
       </c>
       <c r="B77" t="n">
-        <v>36.68819808959961</v>
+        <v>19.92350769042969</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>60</v>
+        <v>25.5</v>
       </c>
       <c r="B78" t="n">
-        <v>68.89756011962891</v>
+        <v>26.95417404174805</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>60</v>
+        <v>19.79999923706055</v>
       </c>
       <c r="B79" t="n">
-        <v>67.77277374267578</v>
+        <v>19.95812606811523</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>21.13095283508301</v>
+        <v>20.37218475341797</v>
       </c>
       <c r="B80" t="n">
-        <v>18.17054557800293</v>
+        <v>22.01924514770508</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>22.70000076293945</v>
       </c>
       <c r="B81" t="n">
-        <v>82.60950469970703</v>
+        <v>20.86606025695801</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>22.33104705810547</v>
+        <v>21.5475025177002</v>
       </c>
       <c r="B82" t="n">
-        <v>21.39160346984863</v>
+        <v>20.06609916687012</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>28.7952995300293</v>
+        <v>22.3214282989502</v>
       </c>
       <c r="B83" t="n">
-        <v>30.65286445617676</v>
+        <v>20.75873756408691</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>15.083251953125</v>
+        <v>11.2380952835083</v>
       </c>
       <c r="B84" t="n">
-        <v>12.0068531036377</v>
+        <v>24.79576683044434</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>58</v>
+        <v>13.88888931274414</v>
       </c>
       <c r="B85" t="n">
-        <v>47.14507675170898</v>
+        <v>21.96070289611816</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>24.38785552978516</v>
+        <v>25.95494651794434</v>
       </c>
       <c r="B86" t="n">
-        <v>23.03578948974609</v>
+        <v>27.51033401489258</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>38.39373016357422</v>
+        <v>19.39275169372559</v>
       </c>
       <c r="B87" t="n">
-        <v>36.80747604370117</v>
+        <v>21.57172775268555</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>34.09999847412109</v>
+        <v>87.80000305175781</v>
       </c>
       <c r="B88" t="n">
-        <v>33.04182052612305</v>
+        <v>87.97554016113281</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>100</v>
+        <v>46.5</v>
       </c>
       <c r="B89" t="n">
-        <v>95.52283477783203</v>
+        <v>39.22542190551758</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>31</v>
+        <v>58.70000076293945</v>
       </c>
       <c r="B90" t="n">
-        <v>33.24053192138672</v>
+        <v>48.5771484375</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>13.32027435302734</v>
+        <v>18.31537628173828</v>
       </c>
       <c r="B91" t="n">
-        <v>18.24529075622559</v>
+        <v>11.01190185546875</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>18.70000076293945</v>
+        <v>63.17335891723633</v>
       </c>
       <c r="B92" t="n">
-        <v>20.0245475769043</v>
+        <v>64.25115966796875</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>27.32615089416504</v>
+        <v>42.19047546386719</v>
       </c>
       <c r="B93" t="n">
-        <v>24.85689544677734</v>
+        <v>31.83548545837402</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>36.29999923706055</v>
+        <v>22.13516235351562</v>
       </c>
       <c r="B94" t="n">
-        <v>35.95928573608398</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>23.80952453613281</v>
-      </c>
-      <c r="B95" t="n">
-        <v>17.58242034912109</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>27.79999923706055</v>
-      </c>
-      <c r="B96" t="n">
-        <v>19.83093070983887</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>20.38095283508301</v>
-      </c>
-      <c r="B97" t="n">
-        <v>19.32413673400879</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>12.69841289520264</v>
-      </c>
-      <c r="B98" t="n">
-        <v>10.79112243652344</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>9.027777671813965</v>
-      </c>
-      <c r="B99" t="n">
-        <v>8.75837516784668</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>35.16160583496094</v>
-      </c>
-      <c r="B100" t="n">
-        <v>30.69934463500977</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>13.51616096496582</v>
-      </c>
-      <c r="B101" t="n">
-        <v>14.26145839691162</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>16.56746101379395</v>
-      </c>
-      <c r="B102" t="n">
-        <v>12.26448440551758</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>20.47012710571289</v>
-      </c>
-      <c r="B103" t="n">
-        <v>21.59099006652832</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>42.90000152587891</v>
-      </c>
-      <c r="B104" t="n">
-        <v>44.03602981567383</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>80</v>
-      </c>
-      <c r="B105" t="n">
-        <v>71.31842041015625</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>30.85210609436035</v>
-      </c>
-      <c r="B106" t="n">
-        <v>28.27210235595703</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>23.11459350585938</v>
-      </c>
-      <c r="B107" t="n">
-        <v>23.42572975158691</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>99.20635223388672</v>
-      </c>
-      <c r="B108" t="n">
-        <v>89.33179473876953</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>22.33104705810547</v>
-      </c>
-      <c r="B109" t="n">
-        <v>21.39160346984863</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>20.33730125427246</v>
-      </c>
-      <c r="B110" t="n">
-        <v>18.57882499694824</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>7.242063522338867</v>
-      </c>
-      <c r="B111" t="n">
-        <v>7.795177459716797</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>19.84127044677734</v>
-      </c>
-      <c r="B112" t="n">
-        <v>34.52725219726562</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>27.90476226806641</v>
-      </c>
-      <c r="B113" t="n">
-        <v>27.04875755310059</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>33.70000076293945</v>
-      </c>
-      <c r="B114" t="n">
-        <v>32.55087280273438</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>36.63075256347656</v>
-      </c>
-      <c r="B115" t="n">
-        <v>32.93105316162109</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>68.28571319580078</v>
-      </c>
-      <c r="B116" t="n">
-        <v>66.92156982421875</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>80</v>
-      </c>
-      <c r="B117" t="n">
-        <v>71.33563995361328</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>13.32027435302734</v>
-      </c>
-      <c r="B118" t="n">
-        <v>18.24529075622559</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>10.47430801391602</v>
-      </c>
-      <c r="B119" t="n">
-        <v>10.11770915985107</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>20.27424049377441</v>
-      </c>
-      <c r="B120" t="n">
-        <v>24.09049415588379</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>60.82272338867188</v>
-      </c>
-      <c r="B121" t="n">
-        <v>61.84102630615234</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>33.39862823486328</v>
-      </c>
-      <c r="B122" t="n">
-        <v>30.22053337097168</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>16.39999961853027</v>
-      </c>
-      <c r="B123" t="n">
-        <v>15.55296993255615</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>10.47992134094238</v>
-      </c>
-      <c r="B124" t="n">
-        <v>13.88678932189941</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>58.76591491699219</v>
-      </c>
-      <c r="B125" t="n">
-        <v>57.67932891845703</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>1.469147920608521</v>
-      </c>
-      <c r="B126" t="n">
-        <v>6.91778564453125</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="B127" t="n">
-        <v>13.41403579711914</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>34.70000076293945</v>
-      </c>
-      <c r="B128" t="n">
-        <v>28.41307640075684</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>6.547618865966797</v>
-      </c>
-      <c r="B129" t="n">
-        <v>6.895809173583984</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>19.79999923706055</v>
-      </c>
-      <c r="B130" t="n">
-        <v>23.67647171020508</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>20.80867767333984</v>
-      </c>
-      <c r="B131" t="n">
-        <v>16.04126167297363</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>45.80952453613281</v>
-      </c>
-      <c r="B132" t="n">
-        <v>43.32696533203125</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>13.29365062713623</v>
-      </c>
-      <c r="B133" t="n">
-        <v>12.28902626037598</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>22.3214282989502</v>
-      </c>
-      <c r="B134" t="n">
-        <v>19.9775447845459</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>6.94444465637207</v>
-      </c>
-      <c r="B135" t="n">
-        <v>9.546595573425293</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>25.95494651794434</v>
-      </c>
-      <c r="B136" t="n">
-        <v>24.6032886505127</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>19.39275169372559</v>
-      </c>
-      <c r="B137" t="n">
-        <v>17.78238105773926</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>87.80000305175781</v>
-      </c>
-      <c r="B138" t="n">
-        <v>87.81422424316406</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>26.15083312988281</v>
-      </c>
-      <c r="B139" t="n">
-        <v>24.59866905212402</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="B140" t="n">
-        <v>41.95702743530273</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>27.32615089416504</v>
-      </c>
-      <c r="B141" t="n">
-        <v>24.85689544677734</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>58.70000076293945</v>
-      </c>
-      <c r="B142" t="n">
-        <v>53.57447052001953</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>40.09523773193359</v>
-      </c>
-      <c r="B143" t="n">
-        <v>36.62894821166992</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>80</v>
-      </c>
-      <c r="B144" t="n">
-        <v>76.63645172119141</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>63.17335891723633</v>
-      </c>
-      <c r="B145" t="n">
-        <v>64.51914215087891</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>42.19047546386719</v>
-      </c>
-      <c r="B146" t="n">
-        <v>30.18093299865723</v>
+        <v>20.27704620361328</v>
       </c>
     </row>
   </sheetData>
